--- a/static/standards-correlations/Montana_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Montana_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$61</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Montana CS Standards, adopted Nov 2020, effective July 2021</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Montana CS Standards, adopted Nov 2020, effective July 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1319,7 +1320,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Unit 5.3 teaches version control, repositories, and commits directly. Discovery Systems 13 and 14 assign team roles and manage a project timeline.</t>
+          <t>Unit 5.3 teaches version control, repositories, and commits directly. Introductory Systems 13 and 14 assign team roles and manage a project timeline.</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1406,7 @@
       </c>
       <c r="I23" s="8" t="inlineStr">
         <is>
-          <t>Students plan, build, test, refine, and maintain a versioned program, and Discovery Systems 5 teaches the design cycle. A named software life cycle process is not used.</t>
+          <t>Students plan, build, test, refine, and maintain a versioned program, and Introductory Systems 5 teaches the design cycle. A named software life cycle process is not used.</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1531,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Montana names all three. Students work in a real IDE from PreLab 1, Unit 5.3 teaches repositories, commits, and push and pull, and Discovery Systems 13 assigns rotating team roles.</t>
+          <t>Montana names all three. Students work in a real IDE from PreLab 1, Unit 5.3 teaches repositories, commits, and push and pull, and Introductory Systems 13 assigns rotating team roles.</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2882,7 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3G (Secret Messages / HTTPS) shows credentials exposed over HTTP. Discovery Systems 10 covers phishing as an attack on the person rather than the system.</t>
+          <t>Ext 5.3G (Secret Messages / HTTPS) shows credentials exposed over HTTP. Introductory Systems 10 covers phishing as an attack on the person rather than the system.</t>
         </is>
       </c>
     </row>
@@ -3001,6 +3002,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -3045,7 +3047,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3059,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -3169,6 +3171,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
@@ -3191,7 +3195,7 @@
 SOURCE NOTE: Codes and statements transcribed from the CodeHS published Montana 9-12 framework. Adoption and effective dates verified against OPI. An official PDF and Excel version are available from OPI; verify wording there before any formal submission.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.</t>
         </is>
       </c>
